--- a/new updates/Interview discussion progress.xlsx
+++ b/new updates/Interview discussion progress.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kamalasekaran.s\Documents\Preparation\interview call - schedule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86246E90-D6B3-4C11-9715-772836CACE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FBE516-D9C2-4D93-8C01-D4FC8766C395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
   <si>
     <t>SNO</t>
   </si>
@@ -232,6 +232,12 @@
     <t xml:space="preserve">14-Aug-2026:   Kamal to keep on check mail for  Bank of julius bear main on client interview
 11-Aug-2026:   Kamal to keep on check mail for  Bank of julius bear main on client interview
 </t>
+  </si>
+  <si>
+    <t>Optimum solutions</t>
+  </si>
+  <si>
+    <t>Need to get back after end of the call</t>
   </si>
 </sst>
 </file>
@@ -390,10 +396,10 @@
     <xf numFmtId="15" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="18" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="18" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -675,15 +681,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="53.5703125" customWidth="1"/>
@@ -878,7 +884,7 @@
       <c r="I6" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="20" t="s">
         <v>63</v>
       </c>
       <c r="K6" s="16" t="s">
@@ -1046,38 +1052,38 @@
       </c>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+    <row r="12" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="7">
         <v>7305232493</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="8">
         <v>46247</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="8">
         <v>46251</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="8">
         <v>46252</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="2" t="s">
+      <c r="I12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="K12" s="2"/>
+      <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -1113,7 +1119,7 @@
       <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1122,7 +1128,7 @@
       <c r="C14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="2">
         <v>9867580699</v>
       </c>
       <c r="E14" s="3">
@@ -1144,6 +1150,31 @@
         <v>62</v>
       </c>
       <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2">
+        <v>6363302105</v>
+      </c>
+      <c r="E15" s="3">
+        <v>46254</v>
+      </c>
+      <c r="F15" s="3">
+        <v>46254</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
